--- a/Documentos/base_datos_proyecto.xlsx
+++ b/Documentos/base_datos_proyecto.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jessi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jessi\OneDrive\Documents\GitHub\DoingEconomics_Proyect\Documentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360452B2-61E7-498F-80A2-688FC58B1BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40132D4-1C82-4CCA-9B2C-1A1957A0C147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Nombre del restaurante (Texto)</t>
   </si>
@@ -110,6 +110,15 @@
   </si>
   <si>
     <t>Calificación promedio en Uber Eats (Numérico: 1–5)</t>
+  </si>
+  <si>
+    <t>Barrio (Texto)</t>
+  </si>
+  <si>
+    <t>¿Pertenece a una cadena de restaurantes? (Binaria: Si/No)</t>
+  </si>
+  <si>
+    <t>Idetificador del restaurante (Numérico)</t>
   </si>
 </sst>
 </file>
@@ -518,105 +527,115 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:AG17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="30" width="21.77734375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="17.88671875" customWidth="1"/>
+    <col min="2" max="33" width="21.77734375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -647,8 +666,11 @@
       <c r="AB2" s="3"/>
       <c r="AC2" s="3"/>
       <c r="AD2" s="3"/>
-    </row>
-    <row r="3" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+    </row>
+    <row r="3" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -679,8 +701,11 @@
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
       <c r="AD3" s="4"/>
-    </row>
-    <row r="4" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE3" s="4"/>
+      <c r="AF3" s="4"/>
+      <c r="AG3" s="4"/>
+    </row>
+    <row r="4" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -711,8 +736,11 @@
       <c r="AB4" s="3"/>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
-    </row>
-    <row r="5" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+    </row>
+    <row r="5" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -743,8 +771,11 @@
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
-    </row>
-    <row r="6" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE5" s="4"/>
+      <c r="AF5" s="4"/>
+      <c r="AG5" s="4"/>
+    </row>
+    <row r="6" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -775,8 +806,11 @@
       <c r="AB6" s="3"/>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
-    </row>
-    <row r="7" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+    </row>
+    <row r="7" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -807,8 +841,11 @@
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
       <c r="AD7" s="4"/>
-    </row>
-    <row r="8" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE7" s="4"/>
+      <c r="AF7" s="4"/>
+      <c r="AG7" s="4"/>
+    </row>
+    <row r="8" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -839,8 +876,11 @@
       <c r="AB8" s="3"/>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
-    </row>
-    <row r="9" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="3"/>
+    </row>
+    <row r="9" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -871,8 +911,11 @@
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
-    </row>
-    <row r="10" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE9" s="4"/>
+      <c r="AF9" s="4"/>
+      <c r="AG9" s="4"/>
+    </row>
+    <row r="10" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -903,8 +946,11 @@
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
-    </row>
-    <row r="11" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="3"/>
+    </row>
+    <row r="11" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -935,8 +981,11 @@
       <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
-    </row>
-    <row r="12" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE11" s="4"/>
+      <c r="AF11" s="4"/>
+      <c r="AG11" s="4"/>
+    </row>
+    <row r="12" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -967,8 +1016,11 @@
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
-    </row>
-    <row r="13" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3"/>
+    </row>
+    <row r="13" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -999,8 +1051,11 @@
       <c r="AB13" s="4"/>
       <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
-    </row>
-    <row r="14" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE13" s="4"/>
+      <c r="AF13" s="4"/>
+      <c r="AG13" s="4"/>
+    </row>
+    <row r="14" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1031,8 +1086,11 @@
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
-    </row>
-    <row r="15" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE14" s="3"/>
+      <c r="AF14" s="3"/>
+      <c r="AG14" s="3"/>
+    </row>
+    <row r="15" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1063,8 +1121,11 @@
       <c r="AB15" s="4"/>
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
-    </row>
-    <row r="16" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE15" s="4"/>
+      <c r="AF15" s="4"/>
+      <c r="AG15" s="4"/>
+    </row>
+    <row r="16" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1095,11 +1156,11 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="12:30" x14ac:dyDescent="0.3">
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="15:33" x14ac:dyDescent="0.3">
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
@@ -1116,6 +1177,9 @@
       <c r="AB17" s="4"/>
       <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
+      <c r="AE17" s="4"/>
+      <c r="AF17" s="4"/>
+      <c r="AG17" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
